--- a/entity_plans/92 HYDROLOGISTS REGISTRATION BOARD.xlsx
+++ b/entity_plans/92 HYDROLOGISTS REGISTRATION BOARD.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -105,11 +105,24 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -478,13 +491,13 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="69" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="69" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -541,378 +554,778 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Live Plant &amp; Animal Material &amp; Accessories &amp; Supplies</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Management &amp; Business Professionals &amp; Administrative Services</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>5600000</v>
       </c>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>RFQ/RFQ YOUTH</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Editorial &amp; Design &amp; Graphic &amp; Fine Art Services</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>2000000</v>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Education &amp; Training Services</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>3400000</v>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Information Technology Broadcasting &amp; Telecommunications</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>4657000</v>
       </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN/RFQ YOUTH/RFQ PWD</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>RFQ/RFQ WOMEN/RFQ PWD</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>RFQ/RFQ PWD</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Paper Materials &amp; Products</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>104070</v>
       </c>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH/RFQ PWD</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Office Equipment &amp; Accessories &amp; Supplies</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>406886</v>
       </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH/RFQ PWD</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Published Products</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>42100</v>
       </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH/RFQ PWD</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Manufacturing Components &amp; Supplies</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="5" t="n">
         <v>2220</v>
       </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Power Generation &amp; Distribution Machinery &amp; Accessories</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="5" t="n">
         <v>12000</v>
       </c>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Service Industry Machinery &amp; Equipment &amp; Supplies</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>32000</v>
       </c>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>RFQ PWD</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Laboratory &amp; Measuring &amp; Observing &amp; Testing Equipment</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Defense &amp; Law Enforcement &amp; Security &amp; Safety Equipment &amp; Supplies</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="5" t="n">
         <v>48501</v>
       </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>RFQ PWD</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Furniture &amp; Furnishings</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="5" t="n">
         <v>618800</v>
       </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH/RFQ PWD</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Financial &amp; Insurance Services</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="5" t="n">
         <v>900000</v>
       </c>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Travel &amp; Food &amp; Lodging &amp; Entertainment Services</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="5" t="n">
         <v>1500000</v>
       </c>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Fuels &amp; Fuel Additives &amp; Lubricants &amp; Anti corrosive Materials</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="5" t="n">
         <v>800000</v>
       </c>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Transportation &amp; Storage &amp; Mail Services</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Domestic Appliances &amp; Supplies &amp; Consumer Electronic Products</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Apparel &amp; Luggage &amp; Personal Care Products</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="5" t="n">
         <v>16000</v>
       </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>RFQ AGPO</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>RFQ PWD</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="7">
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="8">
         <f>SUM(C3:C22)</f>
         <v/>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
